--- a/Dataset/1_label/DOWN_DOWN_V5_50 divisions_per_second.xlsx
+++ b/Dataset/1_label/DOWN_DOWN_V5_50 divisions_per_second.xlsx
@@ -1234,7 +1234,7 @@
         <v>10400</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>10600</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>10800</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>11000</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>11200</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>11400</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>11600</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>11800</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>12000</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>12200</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
